--- a/stories/arbres/ATOM-SEC.PAR.001-09.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-09.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Clovis est au parc. Maman tient sa main. Le bac à sable est là. Maman montre l'espace. C'est l'espace montré. Clovis s'assoit dans le bac. Il sent le sable. Le sable est frais. Maman s'assoit sur le banc. L'adulte voit Clovis. Maman voit. Clovis verse le sable. Le seau est rouge. Il reste dans l'espace montré. Maman dit : je te vois. L'adulte voit. Clovis creuse. Il reste là. Près de maman. Papa arrivera plus tard. Clovis joue ici.</t>
+          <t>Clovis est au parc. Maman tient sa main. Le bac à sable est là. Maman montre l'espace. C'est l'espace montré. Clovis s'assoit dans le bac. Il sent le sable. Le sable est frais. Maman s'assoit sur le banc. L'adulte voit Clovis. Maman voit. Clovis verse le sable. Le seau est rouge. Il reste dans l'espace montré. Je te vois. L'adulte voit. Clovis creuse. Il reste là. Près de maman. Papa arrivera plus tard. Clovis joue ici.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Clovis est au parc. Maman tient sa main. Le bac à sable est là. Maman montre l'espace. C'est l'espace montré. Clovis s'assoit dans le bac. Il sent le sable. Le sable est frais. Maman s'assoit sur le banc. L'adulte voit Clovis. Maman voit. Clovis verse le sable. Le seau est rouge. Il reste dans l'espace montré.
+maman|Je te vois. L'adulte voit.
+narrateur|Clovis creuse. Il reste là. Près de maman. Papa arrivera plus tard. Clovis joue ici.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Clovis joue au parc. Où reste-t-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Clovis est dans l'espace montré. Maman, l'adulte, voit. Le sable reste dans le bac.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1828,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Clovis range le seau. Maman lui tend la main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1995,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-09.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-09.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,11 @@
 narrateur|Clovis creuse. Il reste là. Près de maman. Papa arrivera plus tard. Clovis joue ici.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1493,6 +1503,11 @@
       <c r="AW3" t="inlineStr">
         <is>
           <t>narrateur|Clovis joue au parc. Où reste-t-il ?</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
         </is>
       </c>
     </row>
@@ -1666,6 +1681,7 @@
           <t>narrateur|Clovis est dans l'espace montré. Maman, l'adulte, voit. Le sable reste dans le bac.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1849,7 @@
           <t>narrateur|Clovis range le seau. Maman lui tend la main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2017,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2060,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2275,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.PAR.001-09.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-09.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Clovis joue où maman voit</t>
+          <t>Le seau rouge de Nino</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nino verse le sable du seau rouge dans l'espace que maman a montré. Maman voit.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Clovis est au parc. Maman tient sa main. Le bac à sable est là. Maman montre l'espace. C'est l'espace montré. Clovis s'assoit dans le bac. Il sent le sable. Le sable est frais. Maman s'assoit sur le banc. L'adulte voit Clovis. Maman voit. Clovis verse le sable. Le seau est rouge. Il reste dans l'espace montré. Je te vois. L'adulte voit. Clovis creuse. Il reste là. Près de maman. Papa arrivera plus tard. Clovis joue ici.</t>
+          <t>Un grain de sable brille au soleil. Le parc sent l'herbe chaude. Un seau rouge attend dans le bac. Une abeille visite une fleur jaune. Le banc est chaud sous la main. Maman tient la main de Nino. Tu as vu le grain, Nino ? Oui, maman. Il brille. En ce moment, le bac à sable est là. Maman montre l'espace. C'est l'espace montré. Tu joues ici. L'adulte voit. Ici ? Oui. Dans l'espace montré. Nino s'assoit dans le bac. Il sent le sable. Le sable est frais. Maman s'assoit sur le banc. L'adulte voit Nino. Maman voit. Nino verse le sable. Le seau est rouge. Il reste dans l'espace montré. Je te vois. L'adulte voit. Tu me vois ? Oui. Tu es ici. Nino creuse. Il reste là. Près de maman. Le sable colle aux doigts. C'est mou. Oui. Le sable est frais. Tu restes dans l'espace montré ? Oui. Ici. Bravo, Nino. Tu as fait du bon travail. Nino remplit encore le seau. Le seau rouge est lourd. Il verse tout doucement. Le tas est petit et rond. Tu joues là où l'adulte a dit. Là où l'adulte a dit. Oui. Une abeille part vers la haie. Nino reste dans l'espace montré. L'adulte voit. Tu as fini le tas ? Encore un peu. Nino lisse le tas. Il reste près du banc. Maman le voit. L'adulte voit. Le grain de sable brille encore. Nino pose la main dessus. Il est chaud. Oui. Le soleil le chauffe. Nino recouvre le grain. Le tas devient un peu plus gros. Tu restes ici ? Oui. Dans l'espace montré. Bravo. Le seau rouge penche un peu. Nino le redresse. Il reste dans l'espace montré. L'adulte voit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,9 +1324,80 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Clovis est au parc. Maman tient sa main. Le bac à sable est là. Maman montre l'espace. C'est l'espace montré. Clovis s'assoit dans le bac. Il sent le sable. Le sable est frais. Maman s'assoit sur le banc. L'adulte voit Clovis. Maman voit. Clovis verse le sable. Le seau est rouge. Il reste dans l'espace montré.
-maman|Je te vois. L'adulte voit.
-narrateur|Clovis creuse. Il reste là. Près de maman. Papa arrivera plus tard. Clovis joue ici.</t>
+          <t>narrateur|Un grain de sable brille au soleil.
+narrateur|Le parc sent l'herbe chaude.
+narrateur|Un seau rouge attend dans le bac.
+narrateur|Une abeille visite une fleur jaune.
+narrateur|Le banc est chaud sous la main.
+narrateur|Maman tient la main de Nino.
+maman|Tu as vu le grain, Nino ?
+enfant-m|Oui, maman.
+enfant-m|Il brille.
+narrateur|En ce moment, le bac à sable est là.
+narrateur|Maman montre l'espace.
+maman|C'est l'espace montré.
+maman|Tu joues ici.
+maman|L'adulte voit.
+enfant-m|Ici ?
+maman|Oui.
+maman|Dans l'espace montré.
+narrateur|Nino s'assoit dans le bac.
+narrateur|Il sent le sable.
+narrateur|Le sable est frais.
+narrateur|Maman s'assoit sur le banc.
+narrateur|L'adulte voit Nino.
+narrateur|Maman voit.
+narrateur|Nino verse le sable.
+narrateur|Le seau est rouge.
+narrateur|Il reste dans l'espace montré.
+maman|Je te vois.
+maman|L'adulte voit.
+enfant-m|Tu me vois ?
+maman|Oui.
+maman|Tu es ici.
+narrateur|Nino creuse.
+narrateur|Il reste là.
+narrateur|Près de maman.
+narrateur|Le sable colle aux doigts.
+enfant-m|C'est mou.
+maman|Oui.
+maman|Le sable est frais.
+maman|Tu restes dans l'espace montré ?
+enfant-m|Oui.
+enfant-m|Ici.
+maman|Bravo, Nino.
+maman|Tu as fait du bon travail.
+narrateur|Nino remplit encore le seau.
+narrateur|Le seau rouge est lourd.
+narrateur|Il verse tout doucement.
+narrateur|Le tas est petit et rond.
+maman|Tu joues là où l'adulte a dit.
+enfant-m|Là où l'adulte a dit.
+maman|Oui.
+narrateur|Une abeille part vers la haie.
+narrateur|Nino reste dans l'espace montré.
+narrateur|L'adulte voit.
+maman|Tu as fini le tas ?
+enfant-m|Encore un peu.
+narrateur|Nino lisse le tas.
+narrateur|Il reste près du banc.
+narrateur|Maman le voit.
+narrateur|L'adulte voit.
+narrateur|Le grain de sable brille encore.
+narrateur|Nino pose la main dessus.
+enfant-m|Il est chaud.
+maman|Oui.
+maman|Le soleil le chauffe.
+narrateur|Nino recouvre le grain.
+narrateur|Le tas devient un peu plus gros.
+maman|Tu restes ici ?
+enfant-m|Oui.
+enfant-m|Dans l'espace montré.
+maman|Bravo.
+narrateur|Le seau rouge penche un peu.
+narrateur|Nino le redresse.
+narrateur|Il reste dans l'espace montré.
+narrateur|L'adulte voit.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1346,7 +1429,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Clovis joue au parc. Où reste-t-il ?</t>
+          <t>Nino joue au parc. Où reste-t-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1585,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Clovis joue au parc. Où reste-t-il ?</t>
+          <t>narrateur|Nino joue au parc.
+narrateur|Où reste-t-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1534,7 +1618,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Clovis est dans l'espace montré. Maman, l'adulte, voit. Le sable reste dans le bac.</t>
+          <t>Nino est dans l'espace montré. Maman, l'adulte, voit. Le sable reste dans le bac. Tu es resté dans l'espace montré ? Oui. Bravo. L'adulte voit. Le seau rouge est encore là.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,7 +1762,14 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Clovis est dans l'espace montré. Maman, l'adulte, voit. Le sable reste dans le bac.</t>
+          <t>narrateur|Nino est dans l'espace montré.
+narrateur|Maman, l'adulte, voit.
+narrateur|Le sable reste dans le bac.
+maman|Tu es resté dans l'espace montré ?
+enfant-m|Oui.
+maman|Bravo.
+maman|L'adulte voit.
+narrateur|Le seau rouge est encore là.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1706,7 +1797,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Clovis range le seau. Maman lui tend la main.</t>
+          <t>Nino range le seau. Le sable tombe, tout fin. Tu as fini de ranger ? Oui, maman. Bravo. Maman lui tend la main. Papa arrive sur le chemin. Tu as joué ici ? Oui, papa. Dans l'espace montré. L'adulte voit.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1846,7 +1937,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Clovis range le seau. Maman lui tend la main.</t>
+          <t>narrateur|Nino range le seau.
+narrateur|Le sable tombe, tout fin.
+maman|Tu as fini de ranger ?
+enfant-m|Oui, maman.
+maman|Bravo.
+narrateur|Maman lui tend la main.
+narrateur|Papa arrive sur le chemin.
+papa|Tu as joué ici ?
+enfant-m|Oui, papa.
+papa|Dans l'espace montré.
+maman|L'adulte voit.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1874,7 +1975,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nino tient la main de maman. On a fait un tas. Oui. Dans l'espace montré. Bravo, Nino. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2014,7 +2115,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nino tient la main de maman.
+enfant-m|On a fait un tas.
+maman|Oui.
+maman|Dans l'espace montré.
+maman|Bravo, Nino.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2036,7 +2142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2074,6 +2180,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-09.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-09.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un grain de sable brille au soleil. Le parc sent l'herbe chaude. Un seau rouge attend dans le bac. Une abeille visite une fleur jaune. Le banc est chaud sous la main. Maman tient la main de Nino. Tu as vu le grain, Nino ? Oui, maman. Il brille. En ce moment, le bac à sable est là. Maman montre l'espace. C'est l'espace montré. Tu joues ici. L'adulte voit. Ici ? Oui. Dans l'espace montré. Nino s'assoit dans le bac. Il sent le sable. Le sable est frais. Maman s'assoit sur le banc. L'adulte voit Nino. Maman voit. Nino verse le sable. Le seau est rouge. Il reste dans l'espace montré. Je te vois. L'adulte voit. Tu me vois ? Oui. Tu es ici. Nino creuse. Il reste là. Près de maman. Le sable colle aux doigts. C'est mou. Oui. Le sable est frais. Tu restes dans l'espace montré ? Oui. Ici. Bravo, Nino. Tu as fait du bon travail. Nino remplit encore le seau. Le seau rouge est lourd. Il verse tout doucement. Le tas est petit et rond. Tu joues là où l'adulte a dit. Là où l'adulte a dit. Oui. Une abeille part vers la haie. Nino reste dans l'espace montré. L'adulte voit. Tu as fini le tas ? Encore un peu. Nino lisse le tas. Il reste près du banc. Maman le voit. L'adulte voit. Le grain de sable brille encore. Nino pose la main dessus. Il est chaud. Oui. Le soleil le chauffe. Nino recouvre le grain. Le tas devient un peu plus gros. Tu restes ici ? Oui. Dans l'espace montré. Bravo. Le seau rouge penche un peu. Nino le redresse. Il reste dans l'espace montré. L'adulte voit.</t>
+          <t>Un grain de sable brille au soleil. Le parc sent l'herbe chaude. Un seau rouge attend dans le bac. Une abeille visite une fleur jaune. Le banc est chaud sous la main. Maman tient la main de Nino. Tu as vu le grain, Nino ? Oui, maman. Il brille. En ce moment, le bac à sable est là. Maman montre l'espace. C'est l'espace montré. Tu joues ici. L'adulte voit. Ici ? Oui. Dans l'espace montré. Nino s'assoit dans le bac. Il sent le sable. Le sable est frais. Maman s'assoit sur le banc. L'adulte voit Nino. Maman voit. Nino verse le sable. Le seau est rouge. Il reste dans l'espace montré. Je te vois. L'adulte voit. Tu me vois ? Oui. Tu es ici. Nino creuse. Il reste là. Près de maman. Le sable colle aux doigts. C'est mou. Oui. Le sable est frais. Tu restes dans l'espace montré ? Oui. Ici. Bravo, Nino. Nino remplit encore le seau. Le seau rouge est lourd. Il verse tout doucement. Le tas est petit et rond. Tu joues là où l'adulte a dit. Là où l'adulte a dit. Oui. Une abeille part vers la haie. Nino reste dans l'espace montré. L'adulte voit. Tu as fini le tas ? Encore un peu. Nino lisse le tas. Il reste près du banc. Maman le voit. L'adulte voit. Le grain de sable brille encore. Nino pose la main dessus. Il est chaud. Oui. Le soleil le chauffe. Nino recouvre le grain. Le tas devient un peu plus gros. Tu restes ici ? Oui. Dans l'espace montré. Bravo. Le seau rouge penche un peu. Nino le redresse. Il reste dans l'espace montré. L'adulte voit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Clovis est au parc. Maman tient sa main. Le bac à sable est là. Maman montre l'&lt;emphasis level="moderate"&gt;espace&lt;/emphasis&gt;. C'est l'espace montré. Clovis s'assoit dans le bac. Il sent le sable. Le sable est frais. Maman s'assoit sur le banc. L'adulte voit Clovis. Maman voit. Clovis verse le sable. Le seau est rouge. Il reste dans l'espace montré. Maman dit : je te vois. L'adulte voit. Clovis creuse. Il reste là. Près de maman. Papa arrivera plus tard. Clovis joue ici.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un grain de sable brille au soleil. Le parc sent l'herbe chaude. Un seau rouge attend dans le bac. Une abeille visite une fleur jaune. Le banc est chaud sous la main. Maman tient la main de Nino. Tu as vu le grain, Nino ? Oui, maman. Il brille. En ce moment, le bac à sable est là. Maman montre l'espace. C'est l'espace montré. Tu joues ici. L'adulte voit. Ici ? Oui. Dans l'espace montré. Nino s'assoit dans le bac. Il sent le sable. Le sable est frais. Maman s'assoit sur le banc. L'adulte voit Nino. Maman voit. Nino verse le sable. Le seau est rouge. Il reste dans l'espace montré. Je te vois. L'adulte voit. Tu me vois ? Oui. Tu es ici. Nino creuse. Il reste là. Près de maman. Le sable colle aux doigts. C'est mou. Oui. Le sable est frais. Tu restes dans l'espace montré ? Oui. Ici. Bravo, Nino. Nino remplit encore le seau. Le seau rouge est lourd. Il verse tout doucement. Le tas est petit et rond. Tu joues là où l'adulte a dit. Là où l'adulte a dit. Oui. Une abeille part vers la haie. Nino reste dans l'espace montré. L'adulte voit. Tu as fini le tas ? Encore un peu. Nino lisse le tas. Il reste près du banc. Maman le voit. L'adulte voit. Le grain de sable brille encore. Nino pose la main dessus. Il est chaud. Oui. Le soleil le chauffe. Nino recouvre le grain. Le tas devient un peu plus gros. Tu restes ici ? Oui. Dans l'espace montré. Bravo. Le seau rouge penche un peu. Nino le redresse. Il reste dans l'espace montré. L'adulte voit.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1366,7 +1366,6 @@
 enfant-m|Oui.
 enfant-m|Ici.
 maman|Bravo, Nino.
-maman|Tu as fait du bon travail.
 narrateur|Nino remplit encore le seau.
 narrateur|Le seau rouge est lourd.
 narrateur|Il verse tout doucement.
@@ -1434,7 +1433,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Clovis joue au parc. Où reste-t-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino joue au parc. Où reste-t-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1623,7 +1622,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Clovis est dans l'&lt;emphasis level="moderate"&gt;espace&lt;/emphasis&gt; montré. Maman, l'adulte, voit. Le sable reste dans le bac.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino est dans l'espace montré. Maman, l'adulte, voit. Le sable reste dans le bac. Tu es resté dans l'espace montré ? Oui. Bravo. L'adulte voit. Le seau rouge est encore là.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1772,7 +1771,6 @@
 narrateur|Le seau rouge est encore là.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1802,7 +1800,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Clovis range le seau. Maman lui tend la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino range le seau. Le sable tombe, tout fin. Tu as fini de ranger ? Oui, maman. Bravo. Maman lui tend la main. Papa arrive sur le chemin. Tu as joué ici ? Oui, papa. Dans l'espace montré. L'adulte voit.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1950,7 +1948,6 @@
 maman|L'adulte voit.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1975,12 +1972,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Nino tient la main de maman. On a fait un tas. Oui. Dans l'espace montré. Bravo, Nino. L'histoire est finie.</t>
+          <t>Nino tient la main de maman. On a fait un tas. Oui. Dans l'espace montré. Bravo, Nino.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino tient la main de maman. On a fait un tas. Oui. Dans l'espace montré. Bravo, Nino.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2119,11 +2116,9 @@
 enfant-m|On a fait un tas.
 maman|Oui.
 maman|Dans l'espace montré.
-maman|Bravo, Nino.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|Bravo, Nino.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2142,7 +2137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2187,6 +2182,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-09.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-09.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Clovis, maman</t>
+          <t>Nino, maman, papa</t>
         </is>
       </c>
     </row>
